--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_up_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_up_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>26-01-2021 08:30</t>
+          <t>2021-01-26 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>26-01-2021 08:30</t>
+          <t>2021-01-26 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>26-01-2021 08:30</t>
+          <t>2021-01-26 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>28-02-2021 08:30</t>
+          <t>2021-02-28 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>21-03-2021 08:30</t>
+          <t>2021-03-21 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>28-02-2021 08:30</t>
+          <t>2021-02-28 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>21-03-2021 08:30</t>
+          <t>2021-03-21 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>28-02-2021 08:30</t>
+          <t>2021-02-28 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>21-03-2021 08:30</t>
+          <t>2021-03-21 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12602,7 +12602,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13160,7 +13160,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15375,7 +15375,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -15763,7 +15763,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16167,7 +16167,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -16911,7 +16911,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>26-01-2021 08:30</t>
+          <t>2021-01-26 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>23-09-2021 08:30</t>
+          <t>2021-09-23 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18035,7 +18035,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>23-09-2021 08:30</t>
+          <t>2021-09-23 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>26-11-2021 08:30</t>
+          <t>2021-11-26 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>15-06-2021 08:30</t>
+          <t>2021-06-15 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19304,7 +19304,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19405,7 +19405,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>24-10-2021 08:30</t>
+          <t>2021-10-24 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>26-01-2021 08:30</t>
+          <t>2021-01-26 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -19987,7 +19987,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20278,7 +20278,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20371,7 +20371,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20559,7 +20559,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>02-04-2021 08:30</t>
+          <t>2021-02-04 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -20844,7 +20844,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21129,7 +21129,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21507,7 +21507,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21600,7 +21600,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -21879,7 +21879,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -21972,7 +21972,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22158,7 +22158,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>24-05-2021 08:30</t>
+          <t>2021-05-24 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>30-06-2021 08:30</t>
+          <t>2021-06-30 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="n">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23106,7 +23106,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23484,7 +23484,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23577,7 +23577,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23670,7 +23670,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23763,7 +23763,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24321,7 +24321,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24414,7 +24414,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24507,7 +24507,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr"/>
@@ -24600,7 +24600,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr"/>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr"/>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr"/>
@@ -25158,7 +25158,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25251,7 +25251,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25344,7 +25344,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25437,7 +25437,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>28-02-2021 08:30</t>
+          <t>2021-02-28 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>21-03-2021 08:30</t>
+          <t>2021-03-21 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -25995,7 +25995,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26088,7 +26088,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26460,7 +26460,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26646,7 +26646,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -26832,7 +26832,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -26925,7 +26925,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -27018,7 +27018,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27111,7 +27111,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27204,7 +27204,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="inlineStr"/>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -27483,7 +27483,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -27576,7 +27576,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -27669,7 +27669,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -27762,7 +27762,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -27855,7 +27855,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -27948,7 +27948,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28041,7 +28041,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28320,7 +28320,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28413,7 +28413,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28506,7 +28506,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -28599,7 +28599,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -28692,7 +28692,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -28785,7 +28785,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -28878,7 +28878,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -28971,7 +28971,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29157,7 +29157,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="inlineStr"/>
@@ -29250,7 +29250,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="inlineStr"/>
@@ -29343,7 +29343,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="inlineStr"/>
@@ -29436,7 +29436,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="inlineStr"/>
@@ -29529,7 +29529,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="inlineStr"/>
@@ -29622,7 +29622,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="inlineStr"/>
@@ -29715,7 +29715,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -29808,7 +29808,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30087,7 +30087,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30180,7 +30180,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30366,7 +30366,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30459,7 +30459,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -30831,7 +30831,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="inlineStr"/>
@@ -30924,7 +30924,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -31017,7 +31017,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="inlineStr"/>
@@ -31110,7 +31110,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -31203,7 +31203,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="inlineStr"/>
@@ -31296,7 +31296,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31389,7 +31389,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -31668,7 +31668,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -31854,7 +31854,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -31947,7 +31947,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32040,7 +32040,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32226,7 +32226,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32319,7 +32319,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32505,7 +32505,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32598,7 +32598,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -32691,7 +32691,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -32784,7 +32784,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -32970,7 +32970,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33063,7 +33063,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33249,7 +33249,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>25-05-2021 08:30</t>
+          <t>2021-05-25 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="n">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="n">
@@ -33447,7 +33447,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33540,7 +33540,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -33633,7 +33633,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="inlineStr"/>
@@ -33726,7 +33726,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34201,7 +34201,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34391,7 +34391,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="inlineStr"/>
@@ -34674,7 +34674,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="inlineStr"/>
@@ -34767,7 +34767,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -34866,7 +34866,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35068,7 +35068,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35262,7 +35262,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -35355,7 +35355,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -35448,7 +35448,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -35541,7 +35541,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -35634,7 +35634,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -35727,7 +35727,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -35820,7 +35820,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -35913,7 +35913,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36006,7 +36006,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36192,7 +36192,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36285,7 +36285,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36378,7 +36378,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -36471,7 +36471,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -36564,7 +36564,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -36657,7 +36657,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -36750,7 +36750,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -36843,7 +36843,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -36936,7 +36936,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37122,7 +37122,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="inlineStr"/>
@@ -37215,7 +37215,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="inlineStr"/>
@@ -37308,7 +37308,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="inlineStr"/>
@@ -37401,7 +37401,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="inlineStr"/>
@@ -37494,7 +37494,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="inlineStr"/>
@@ -37587,7 +37587,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="inlineStr"/>
@@ -37680,7 +37680,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="inlineStr"/>
@@ -37773,7 +37773,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="inlineStr"/>
@@ -37866,7 +37866,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="inlineStr"/>
@@ -37959,7 +37959,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="inlineStr"/>
@@ -38052,7 +38052,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="inlineStr"/>
@@ -38145,7 +38145,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="inlineStr"/>
